--- a/data/trans_dic/P36B06_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,06; 77,19</t>
+          <t>65,91; 76,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,32; 79,52</t>
+          <t>69,61; 79,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,49; 80,94</t>
+          <t>70,98; 80,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75,07; 85,43</t>
+          <t>74,25; 84,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,79; 82,19</t>
+          <t>72,0; 82,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,94; 85,15</t>
+          <t>75,96; 85,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,01; 79,55</t>
+          <t>72,0; 79,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>72,3; 79,6</t>
+          <t>72,21; 79,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,57; 81,74</t>
+          <t>74,97; 81,97</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,12; 75,49</t>
+          <t>67,01; 75,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,72; 88,31</t>
+          <t>81,72; 88,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,27; 88,59</t>
+          <t>82,43; 88,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69,24; 77,2</t>
+          <t>69,32; 77,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,62; 90,37</t>
+          <t>84,66; 90,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,84; 93,83</t>
+          <t>88,97; 93,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,48; 75,16</t>
+          <t>69,51; 75,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,19; 88,59</t>
+          <t>84,46; 88,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,61; 90,57</t>
+          <t>86,27; 90,44</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75,67; 85,0</t>
+          <t>75,45; 84,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,13; 91,1</t>
+          <t>84,37; 91,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,3; 87,27</t>
+          <t>79,39; 87,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,18; 92,71</t>
+          <t>86,46; 92,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,77; 95,55</t>
+          <t>89,64; 95,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,94; 90,03</t>
+          <t>82,44; 89,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,43; 88,07</t>
+          <t>82,33; 87,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88,17; 92,73</t>
+          <t>87,94; 92,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,68; 88,08</t>
+          <t>82,22; 87,82</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,38; 86,98</t>
+          <t>79,43; 87,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,87; 86,41</t>
+          <t>77,93; 86,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,71; 83,74</t>
+          <t>75,76; 84,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,51; 92,65</t>
+          <t>87,0; 92,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,07; 95,25</t>
+          <t>89,87; 95,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,14; 89,14</t>
+          <t>81,73; 89,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,33; 89,22</t>
+          <t>84,15; 89,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,03; 89,91</t>
+          <t>84,82; 89,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>79,98; 85,64</t>
+          <t>80,19; 85,79</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>58,9; 72,23</t>
+          <t>59,06; 71,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,81; 80,65</t>
+          <t>67,08; 80,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,64; 94,79</t>
+          <t>86,35; 94,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,93; 77,06</t>
+          <t>64,04; 76,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,16; 91,2</t>
+          <t>81,95; 91,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,89; 96,66</t>
+          <t>90,52; 96,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,34; 72,56</t>
+          <t>63,53; 72,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>76,44; 84,45</t>
+          <t>76,6; 84,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,77; 94,88</t>
+          <t>89,89; 95,09</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,97; 86,37</t>
+          <t>76,81; 86,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,17; 92,6</t>
+          <t>85,15; 92,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,29; 67,31</t>
+          <t>55,51; 67,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79,28; 87,74</t>
+          <t>78,91; 87,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84,4; 92,86</t>
+          <t>84,83; 92,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,53; 71,26</t>
+          <t>58,74; 71,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,64; 85,72</t>
+          <t>79,46; 85,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86,19; 91,89</t>
+          <t>86,19; 91,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,02; 67,63</t>
+          <t>58,92; 67,52</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>78,17; 84,53</t>
+          <t>78,02; 84,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,21; 87,7</t>
+          <t>82,07; 87,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,56; 76,17</t>
+          <t>68,31; 75,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,69; 88,26</t>
+          <t>82,79; 88,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,96; 90,18</t>
+          <t>84,72; 90,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,71; 78,7</t>
+          <t>71,99; 78,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,48; 85,79</t>
+          <t>81,5; 85,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,43; 88,43</t>
+          <t>84,64; 88,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,35; 76,23</t>
+          <t>71,12; 76,22</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>68,64; 75,17</t>
+          <t>68,7; 75,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,22; 85,63</t>
+          <t>80,33; 85,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,83; 88,55</t>
+          <t>83,7; 88,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75,86; 81,62</t>
+          <t>75,72; 81,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,79; 88,84</t>
+          <t>83,67; 88,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,48; 88,46</t>
+          <t>83,62; 88,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,11; 77,68</t>
+          <t>73,27; 77,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>82,87; 86,54</t>
+          <t>82,81; 86,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84,46; 87,94</t>
+          <t>84,54; 87,93</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,82; 77,73</t>
+          <t>74,89; 77,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>82,2; 84,75</t>
+          <t>81,88; 84,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78,54; 81,24</t>
+          <t>78,62; 81,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,24; 82,89</t>
+          <t>80,35; 82,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86,71; 88,83</t>
+          <t>86,48; 88,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>82,12; 84,59</t>
+          <t>82,13; 84,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,85; 80,03</t>
+          <t>77,96; 80,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84,79; 86,48</t>
+          <t>84,72; 86,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80,71; 82,65</t>
+          <t>80,81; 82,67</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>180337; 210739</t>
+          <t>179935; 209375</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>204298; 234385</t>
+          <t>205169; 235257</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>205640; 236113</t>
+          <t>207074; 236237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>195808; 222831</t>
+          <t>193678; 220857</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>204598; 234238</t>
+          <t>205206; 234980</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>219251; 245844</t>
+          <t>219286; 246345</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>384400; 424665</t>
+          <t>384377; 424971</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>419145; 461486</t>
+          <t>418631; 461671</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>432837; 474422</t>
+          <t>435131; 475753</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>329623; 370712</t>
+          <t>329089; 371771</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>412250; 445532</t>
+          <t>412290; 445741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>413467; 445231</t>
+          <t>414254; 445803</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>348952; 389055</t>
+          <t>349346; 390436</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>443233; 473313</t>
+          <t>443440; 475182</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>464732; 490823</t>
+          <t>465373; 490279</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>691395; 747898</t>
+          <t>691599; 747257</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>865661; 910904</t>
+          <t>868480; 911773</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>888324; 928927</t>
+          <t>884847; 927569</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>241277; 271006</t>
+          <t>240570; 269738</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>272612; 295192</t>
+          <t>273402; 295564</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>252608; 278017</t>
+          <t>252897; 278921</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>289063; 310956</t>
+          <t>289989; 311415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>305234; 324905</t>
+          <t>304802; 325266</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>278949; 302781</t>
+          <t>277258; 302348</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>539308; 576175</t>
+          <t>538658; 573234</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>585546; 615780</t>
+          <t>583992; 615712</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541418; 576792</t>
+          <t>538413; 575078</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>284726; 311985</t>
+          <t>284910; 313562</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>291210; 323140</t>
+          <t>291436; 321666</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>280115; 309792</t>
+          <t>280302; 310991</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>321361; 344161</t>
+          <t>323149; 344372</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>350343; 370460</t>
+          <t>349533; 370253</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>318129; 345234</t>
+          <t>316517; 345591</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>615711; 651436</t>
+          <t>614381; 649957</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>648733; 685941</t>
+          <t>647118; 685244</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>605648; 648490</t>
+          <t>607221; 649629</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>119752; 146849</t>
+          <t>120064; 146343</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>144171; 171469</t>
+          <t>142629; 170629</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182995; 200207</t>
+          <t>182397; 199804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132766; 160021</t>
+          <t>132989; 159803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>180426; 200276</t>
+          <t>179947; 199819</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>196498; 211279</t>
+          <t>197872; 211449</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>260317; 298217</t>
+          <t>261073; 299728</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>330402; 364995</t>
+          <t>331061; 364397</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>385860; 407797</t>
+          <t>386374; 408689</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>208435; 233906</t>
+          <t>208001; 233848</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>232543; 252829</t>
+          <t>232466; 252338</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>145478; 177107</t>
+          <t>146049; 178656</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>220501; 244032</t>
+          <t>219491; 243608</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>235419; 259026</t>
+          <t>236628; 257961</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>161976; 193909</t>
+          <t>159833; 193494</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>437166; 470576</t>
+          <t>436200; 470742</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>475730; 507204</t>
+          <t>475743; 505939</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>315908; 361999</t>
+          <t>315333; 361406</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>480781; 519879</t>
+          <t>479827; 519554</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>542343; 578573</t>
+          <t>541420; 579045</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>447568; 497236</t>
+          <t>445934; 494493</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>526963; 562446</t>
+          <t>527551; 561693</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>586939; 622967</t>
+          <t>585253; 622720</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>494914; 543151</t>
+          <t>496867; 544324</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1020314; 1074270</t>
+          <t>1020631; 1071446</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1140293; 1194322</t>
+          <t>1143134; 1192712</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>958164; 1023803</t>
+          <t>955082; 1023547</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>509970; 558427</t>
+          <t>510364; 558071</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>624993; 667123</t>
+          <t>625819; 667888</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>651885; 688555</t>
+          <t>650847; 691149</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>593568; 638630</t>
+          <t>592483; 641107</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>690319; 731879</t>
+          <t>689342; 731596</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>686583; 727549</t>
+          <t>687708; 729299</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1115166; 1184919</t>
+          <t>1117657; 1188717</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1328415; 1387272</t>
+          <t>1327345; 1385826</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1351440; 1407097</t>
+          <t>1352658; 1406901</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2449382; 2544630</t>
+          <t>2451498; 2550722</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2812667; 2899943</t>
+          <t>2801621; 2893006</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2660576; 2752130</t>
+          <t>2663191; 2759808</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2709677; 2799375</t>
+          <t>2713392; 2798214</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3078892; 3154466</t>
+          <t>3070752; 3152914</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2905980; 2993329</t>
+          <t>2906414; 2999309</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5177785; 5322608</t>
+          <t>5185270; 5322071</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5912374; 6029929</t>
+          <t>5907117; 6026951</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5590496; 5724540</t>
+          <t>5597182; 5726172</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B06_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36B06_R-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,91; 76,69</t>
+          <t>65,76; 76,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,61; 79,82</t>
+          <t>69,44; 79,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,98; 80,98</t>
+          <t>70,44; 81,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74,25; 84,67</t>
+          <t>74,87; 84,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,0; 82,45</t>
+          <t>71,74; 82,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,96; 85,33</t>
+          <t>75,77; 85,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,0; 79,61</t>
+          <t>72,13; 79,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>72,21; 79,63</t>
+          <t>72,07; 79,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,97; 81,97</t>
+          <t>74,74; 81,99</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,01; 75,7</t>
+          <t>67,44; 75,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,72; 88,36</t>
+          <t>82,05; 88,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,43; 88,7</t>
+          <t>82,17; 88,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69,32; 77,48</t>
+          <t>69,32; 76,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,66; 90,72</t>
+          <t>84,75; 90,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,97; 93,73</t>
+          <t>88,79; 93,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,51; 75,1</t>
+          <t>69,42; 75,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,46; 88,67</t>
+          <t>84,27; 88,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,27; 90,44</t>
+          <t>86,61; 90,68</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75,45; 84,6</t>
+          <t>75,96; 84,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,37; 91,21</t>
+          <t>84,2; 91,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,39; 87,56</t>
+          <t>79,32; 87,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,46; 92,85</t>
+          <t>85,88; 92,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,64; 95,66</t>
+          <t>89,78; 95,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,44; 89,9</t>
+          <t>82,73; 90,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,33; 87,62</t>
+          <t>81,99; 87,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,94; 92,72</t>
+          <t>88,18; 92,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,22; 87,82</t>
+          <t>82,48; 87,91</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,43; 87,42</t>
+          <t>78,84; 87,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,93; 86,01</t>
+          <t>77,47; 86,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,76; 84,06</t>
+          <t>75,08; 84,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,0; 92,71</t>
+          <t>86,73; 92,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,87; 95,19</t>
+          <t>89,86; 94,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,73; 89,23</t>
+          <t>82,14; 89,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,15; 89,02</t>
+          <t>84,38; 89,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,82; 89,82</t>
+          <t>84,68; 89,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>80,19; 85,79</t>
+          <t>80,11; 85,6</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,06; 71,98</t>
+          <t>58,74; 71,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,08; 80,25</t>
+          <t>67,62; 79,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,35; 94,59</t>
+          <t>87,13; 94,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,04; 76,95</t>
+          <t>63,81; 76,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,95; 91,0</t>
+          <t>81,82; 90,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,52; 96,73</t>
+          <t>90,44; 96,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,53; 72,93</t>
+          <t>63,71; 72,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>76,6; 84,31</t>
+          <t>76,28; 84,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,89; 95,09</t>
+          <t>89,94; 94,85</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,81; 86,35</t>
+          <t>76,75; 86,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,15; 92,42</t>
+          <t>85,29; 92,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,51; 67,9</t>
+          <t>55,36; 67,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78,91; 87,58</t>
+          <t>78,99; 87,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84,83; 92,48</t>
+          <t>85,03; 92,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58,74; 71,11</t>
+          <t>58,63; 70,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,46; 85,75</t>
+          <t>79,46; 85,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86,19; 91,66</t>
+          <t>86,18; 91,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58,92; 67,52</t>
+          <t>59,01; 67,79</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>78,02; 84,48</t>
+          <t>77,83; 84,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,07; 87,77</t>
+          <t>82,15; 87,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,31; 75,75</t>
+          <t>68,2; 75,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,79; 88,14</t>
+          <t>82,73; 88,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,72; 90,14</t>
+          <t>84,99; 90,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,99; 78,87</t>
+          <t>72,08; 78,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,5; 85,56</t>
+          <t>81,52; 85,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>84,64; 88,31</t>
+          <t>84,37; 88,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,12; 76,22</t>
+          <t>71,13; 76,33</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>68,7; 75,12</t>
+          <t>68,8; 75,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,33; 85,73</t>
+          <t>79,83; 85,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83,7; 88,88</t>
+          <t>83,63; 88,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75,72; 81,94</t>
+          <t>75,68; 81,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,67; 88,8</t>
+          <t>83,78; 88,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,62; 88,67</t>
+          <t>83,66; 88,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,27; 77,93</t>
+          <t>73,23; 77,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>82,81; 86,45</t>
+          <t>82,92; 86,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84,54; 87,93</t>
+          <t>84,53; 87,92</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,89; 77,92</t>
+          <t>74,74; 77,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>81,88; 84,55</t>
+          <t>82,04; 84,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78,62; 81,47</t>
+          <t>78,63; 81,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80,35; 82,86</t>
+          <t>80,33; 82,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86,48; 88,79</t>
+          <t>86,68; 88,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>82,13; 84,76</t>
+          <t>82,03; 84,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,96; 80,02</t>
+          <t>78,01; 79,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84,72; 86,44</t>
+          <t>84,73; 86,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80,81; 82,67</t>
+          <t>80,73; 82,71</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>179935; 209375</t>
+          <t>179529; 209356</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>205169; 235257</t>
+          <t>204656; 234715</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>207074; 236237</t>
+          <t>205482; 236424</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>193678; 220857</t>
+          <t>195279; 220592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>205206; 234980</t>
+          <t>204451; 234876</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>219286; 246345</t>
+          <t>218761; 246292</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>384377; 424971</t>
+          <t>385053; 426065</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>418631; 461671</t>
+          <t>417832; 461819</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>435131; 475753</t>
+          <t>433840; 475872</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>329089; 371771</t>
+          <t>331164; 370038</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>412290; 445741</t>
+          <t>413926; 446235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>414254; 445803</t>
+          <t>412952; 446072</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>349346; 390436</t>
+          <t>349336; 387540</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>443440; 475182</t>
+          <t>443889; 474652</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>465373; 490279</t>
+          <t>464432; 491571</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>691599; 747257</t>
+          <t>690794; 747394</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>868480; 911773</t>
+          <t>866476; 911591</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>884847; 927569</t>
+          <t>888316; 930024</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>240570; 269738</t>
+          <t>242204; 270319</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>273402; 295564</t>
+          <t>272833; 295687</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>252897; 278921</t>
+          <t>252694; 279095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>289989; 311415</t>
+          <t>288046; 310132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>304802; 325266</t>
+          <t>305293; 325111</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>277258; 302348</t>
+          <t>278227; 303129</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>538658; 573234</t>
+          <t>536441; 574333</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>583992; 615712</t>
+          <t>585600; 615857</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>538413; 575078</t>
+          <t>540122; 575729</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>284910; 313562</t>
+          <t>282774; 312418</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>291436; 321666</t>
+          <t>289714; 321670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>280302; 310991</t>
+          <t>277787; 310766</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>323149; 344372</t>
+          <t>322167; 344331</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>349533; 370253</t>
+          <t>349531; 369420</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>316517; 345591</t>
+          <t>318121; 346289</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>614381; 649957</t>
+          <t>616045; 650276</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>647118; 685244</t>
+          <t>646021; 685227</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>607221; 649629</t>
+          <t>606638; 648190</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>120064; 146343</t>
+          <t>119430; 145486</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>142629; 170629</t>
+          <t>143762; 170077</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182397; 199804</t>
+          <t>184036; 199744</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132989; 159803</t>
+          <t>132520; 159033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>179947; 199819</t>
+          <t>179677; 199407</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>197872; 211449</t>
+          <t>197698; 211467</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>261073; 299728</t>
+          <t>261813; 298534</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>331061; 364397</t>
+          <t>329703; 365063</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>386374; 408689</t>
+          <t>386555; 407692</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>208001; 233848</t>
+          <t>207837; 233959</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>232466; 252338</t>
+          <t>232864; 253029</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>146049; 178656</t>
+          <t>145654; 177255</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>219491; 243608</t>
+          <t>219712; 244418</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>236628; 257961</t>
+          <t>237176; 259104</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>159833; 193494</t>
+          <t>159545; 192843</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>436200; 470742</t>
+          <t>436210; 470036</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>475743; 505939</t>
+          <t>475684; 506021</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>315333; 361406</t>
+          <t>315826; 362821</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>479827; 519554</t>
+          <t>478686; 518008</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>541420; 579045</t>
+          <t>541989; 580173</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>445934; 494493</t>
+          <t>445220; 494722</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>527551; 561693</t>
+          <t>527192; 562061</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>585253; 622720</t>
+          <t>587143; 624142</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>496867; 544324</t>
+          <t>497501; 542781</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1020631; 1071446</t>
+          <t>1020814; 1069135</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1143134; 1192712</t>
+          <t>1139438; 1192001</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>955082; 1023547</t>
+          <t>955215; 1025119</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>510364; 558071</t>
+          <t>511107; 560180</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>625819; 667888</t>
+          <t>621966; 668481</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>650847; 691149</t>
+          <t>650291; 689369</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>592483; 641107</t>
+          <t>592139; 637909</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>689342; 731596</t>
+          <t>690263; 732177</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>687708; 729299</t>
+          <t>688111; 729410</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1117657; 1188717</t>
+          <t>1117026; 1186200</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1327345; 1385826</t>
+          <t>1329185; 1385787</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1352658; 1406901</t>
+          <t>1352594; 1406781</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2451498; 2550722</t>
+          <t>2446669; 2543041</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2801621; 2893006</t>
+          <t>2807106; 2901259</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2663191; 2759808</t>
+          <t>2663723; 2756120</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2713392; 2798214</t>
+          <t>2712791; 2798060</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3070752; 3152914</t>
+          <t>3078052; 3157898</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2906414; 2999309</t>
+          <t>2902820; 2994356</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5185270; 5322071</t>
+          <t>5188156; 5314879</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5907117; 6026951</t>
+          <t>5907769; 6028474</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5597182; 5726172</t>
+          <t>5591746; 5728970</t>
         </is>
       </c>
     </row>
